--- a/lotti/LOTTO_0004.xlsx
+++ b/lotti/LOTTO_0004.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="38">
   <si>
     <t>Order Details</t>
   </si>
@@ -70,37 +70,52 @@
     <t/>
   </si>
   <si>
-    <t>Kit Casa Ajax</t>
-  </si>
-  <si>
-    <t>20262027阿贾克斯主场球迷版</t>
+    <t>Kit Fuori Casa AC Milan</t>
+  </si>
+  <si>
+    <t>20262027米兰客场球迷版</t>
   </si>
   <si>
     <t>Kit</t>
   </si>
   <si>
-    <t>M(QW, 1)</t>
-  </si>
-  <si>
-    <t>M(WQ, 21)</t>
-  </si>
-  <si>
-    <t>Kit Casa AC Milan</t>
-  </si>
-  <si>
-    <t>20262027米兰主场球迷版</t>
-  </si>
-  <si>
-    <t>Kit Casa Arsenal F.C.</t>
-  </si>
-  <si>
-    <t>20262027阿森纳主场球迷版</t>
-  </si>
-  <si>
-    <t>Kit Casa AS Monaco</t>
-  </si>
-  <si>
-    <t>20262027AS Monaco主场球迷版</t>
+    <t>M(PULISIC, 11)</t>
+  </si>
+  <si>
+    <t>Kit Casa Inter</t>
+  </si>
+  <si>
+    <t>20262027国米主场球迷版</t>
+  </si>
+  <si>
+    <t>L(CHALANOGLU, 20)</t>
+  </si>
+  <si>
+    <t>Serie A</t>
+  </si>
+  <si>
+    <t>Kit Casa Barcellona</t>
+  </si>
+  <si>
+    <t>20262027Barcellona主场球迷版</t>
+  </si>
+  <si>
+    <t>M(LAMINE YAMAL, 10)</t>
+  </si>
+  <si>
+    <t>S(ACETO, 4)</t>
+  </si>
+  <si>
+    <t>Kit Casa Argentina</t>
+  </si>
+  <si>
+    <t>20262027阿根廷主场球迷版</t>
+  </si>
+  <si>
+    <t>M(MESSI, 10)</t>
+  </si>
+  <si>
+    <t>mondiali</t>
   </si>
   <si>
     <t>Total Quantity (pcs)</t>
@@ -237,11 +252,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>12000</xdr:colOff>
+      <xdr:colOff>16000</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>20999</xdr:rowOff>
+      <xdr:rowOff>43999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="400050" cy="400050"/>
+    <xdr:ext cx="990600" cy="990600"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -276,11 +291,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>12000</xdr:colOff>
+      <xdr:colOff>16000</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>20999</xdr:rowOff>
+      <xdr:rowOff>43999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="400050" cy="400050"/>
+    <xdr:ext cx="990600" cy="990600"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 2">
@@ -315,11 +330,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>12000</xdr:colOff>
+      <xdr:colOff>16000</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>20999</xdr:rowOff>
+      <xdr:rowOff>43999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="400050" cy="400050"/>
+    <xdr:ext cx="990600" cy="990600"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Picture 3">
@@ -354,11 +369,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>12000</xdr:colOff>
+      <xdr:colOff>16000</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>20999</xdr:rowOff>
+      <xdr:rowOff>43999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="400050" cy="400050"/>
+    <xdr:ext cx="990600" cy="990600"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Picture 4">
@@ -393,11 +408,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>12000</xdr:colOff>
+      <xdr:colOff>16000</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>20999</xdr:rowOff>
+      <xdr:rowOff>43999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="400050" cy="400050"/>
+    <xdr:ext cx="990600" cy="990600"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Picture 5">
@@ -760,7 +775,7 @@
   <dimension ref="A1:Y11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="20" width="6" customWidth="1"/>
@@ -897,7 +912,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
@@ -968,22 +983,22 @@
         <v>18</v>
       </c>
       <c r="X4" s="6">
-        <v>10.3</v>
+        <v>8.86</v>
       </c>
       <c r="Y4" s="6">
         <f>U4*X4</f>
-        <v>10.3</v>
+        <v>8.86</v>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>21</v>
@@ -991,11 +1006,11 @@
       <c r="E5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="5">
         <v>1</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>18</v>
@@ -1040,28 +1055,28 @@
         <v>1</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="X5" s="6">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="Y5" s="6">
         <f>U5*X5</f>
-        <v>10.3</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>21</v>
@@ -1118,7 +1133,7 @@
         <v>1</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="W6" s="4" t="s">
         <v>18</v>
@@ -1131,24 +1146,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="5">
+      <c r="E7" s="5">
         <v>1</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>18</v>
@@ -1196,28 +1211,28 @@
         <v>1</v>
       </c>
       <c r="V7" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="X7" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y7" s="6">
         <f>U7*X7</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" ht="88" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>21</v>
@@ -1274,22 +1289,22 @@
         <v>1</v>
       </c>
       <c r="V8" s="4" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="X8" s="6">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="Y8" s="6">
         <f>U8*X8</f>
-        <v>10.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1316,12 +1331,12 @@
       </c>
       <c r="Y9" s="9">
         <f>SUM(Y4:Y8)</f>
-        <v>50.9</v>
+        <v>51.86</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1343,16 +1358,16 @@
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
       <c r="X10" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Y10" s="9">
         <f>X10*U9</f>
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -1375,7 +1390,7 @@
       <c r="T11" s="7"/>
       <c r="Y11" s="11">
         <f>Y9+Y10</f>
-        <v>70.9</v>
+        <v>96.86</v>
       </c>
     </row>
   </sheetData>
